--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/10.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/10.xlsx
@@ -426,13 +426,13 @@
         <v>-21.6212312038656</v>
       </c>
       <c r="E2">
-        <v>-29.48609865049833</v>
+        <v>-31.78064699510385</v>
       </c>
       <c r="F2">
-        <v>-5.244114956882563</v>
+        <v>-4.978028607500005</v>
       </c>
       <c r="G2">
-        <v>-16.86705190379591</v>
+        <v>-17.97042362657961</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.44483059523249</v>
       </c>
       <c r="E3">
-        <v>-28.68173977607091</v>
+        <v>-31.83101494725417</v>
       </c>
       <c r="F3">
-        <v>-5.143305740541181</v>
+        <v>-4.529519924835722</v>
       </c>
       <c r="G3">
-        <v>-16.45072762841378</v>
+        <v>-19.24043165908251</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.15955729140707</v>
       </c>
       <c r="E4">
-        <v>-28.60273149005908</v>
+        <v>-33.88086719885522</v>
       </c>
       <c r="F4">
-        <v>-4.904935036531771</v>
+        <v>-5.112883541758547</v>
       </c>
       <c r="G4">
-        <v>-15.51191319275064</v>
+        <v>-18.88387100704808</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.77160827302937</v>
       </c>
       <c r="E5">
-        <v>-30.17148545579625</v>
+        <v>-32.37864104476474</v>
       </c>
       <c r="F5">
-        <v>-5.440998900731122</v>
+        <v>-4.521431146872615</v>
       </c>
       <c r="G5">
-        <v>-16.33948336665766</v>
+        <v>-18.75421680154806</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.27388698748021</v>
       </c>
       <c r="E6">
-        <v>-30.34869370066441</v>
+        <v>-33.31217011178696</v>
       </c>
       <c r="F6">
-        <v>-5.088439040953739</v>
+        <v>-5.207922525597026</v>
       </c>
       <c r="G6">
-        <v>-16.96720749326825</v>
+        <v>-19.05269724264152</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.66481857398574</v>
       </c>
       <c r="E7">
-        <v>-31.57632677635178</v>
+        <v>-33.22329428091242</v>
       </c>
       <c r="F7">
-        <v>-5.054179522737996</v>
+        <v>-4.930994125517369</v>
       </c>
       <c r="G7">
-        <v>-16.86742268489631</v>
+        <v>-17.70639437764057</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.95525090768164</v>
       </c>
       <c r="E8">
-        <v>-32.98968389227873</v>
+        <v>-34.5185306808233</v>
       </c>
       <c r="F8">
-        <v>-5.077328552103974</v>
+        <v>-4.54993626964461</v>
       </c>
       <c r="G8">
-        <v>-15.93300796425486</v>
+        <v>-18.22178010719431</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.17478284629235</v>
       </c>
       <c r="E9">
-        <v>-34.52336029835248</v>
+        <v>-33.36607027366325</v>
       </c>
       <c r="F9">
-        <v>-5.149039547808029</v>
+        <v>-4.609489946888795</v>
       </c>
       <c r="G9">
-        <v>-15.00745060820373</v>
+        <v>-19.0070216458362</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.35595094160367</v>
       </c>
       <c r="E10">
-        <v>-33.77514544467215</v>
+        <v>-34.93093654446483</v>
       </c>
       <c r="F10">
-        <v>-5.059548285791335</v>
+        <v>-4.625258906688826</v>
       </c>
       <c r="G10">
-        <v>-15.09643310648103</v>
+        <v>-16.21891991920848</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.52243166158461</v>
       </c>
       <c r="E11">
-        <v>-34.15503912917561</v>
+        <v>-35.35763880054859</v>
       </c>
       <c r="F11">
-        <v>-5.254282348859685</v>
+        <v>-4.58622847440282</v>
       </c>
       <c r="G11">
-        <v>-14.6593450894766</v>
+        <v>-17.53077490260054</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.70124716488756</v>
       </c>
       <c r="E12">
-        <v>-36.12866131356855</v>
+        <v>-35.56616597165379</v>
       </c>
       <c r="F12">
-        <v>-5.099273173121261</v>
+        <v>-4.534599661559494</v>
       </c>
       <c r="G12">
-        <v>-13.67163058565288</v>
+        <v>-17.45160817184718</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.91196592231828</v>
       </c>
       <c r="E13">
-        <v>-34.92568577885294</v>
+        <v>-36.33073314497582</v>
       </c>
       <c r="F13">
-        <v>-5.119462256131283</v>
+        <v>-4.654289819824746</v>
       </c>
       <c r="G13">
-        <v>-13.37202952489438</v>
+        <v>-16.84287830026815</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.19170322235189</v>
       </c>
       <c r="E14">
-        <v>-37.0772634063253</v>
+        <v>-36.38648998119526</v>
       </c>
       <c r="F14">
-        <v>-5.487719017089544</v>
+        <v>-4.844902288248165</v>
       </c>
       <c r="G14">
-        <v>-13.38197771423989</v>
+        <v>-17.52615503630049</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.55600664765898</v>
       </c>
       <c r="E15">
-        <v>-37.54965570090944</v>
+        <v>-37.37599777966329</v>
       </c>
       <c r="F15">
-        <v>-5.175291848915312</v>
+        <v>-4.91115108224987</v>
       </c>
       <c r="G15">
-        <v>-13.54032110738323</v>
+        <v>-15.91206876371897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.00684428270443</v>
       </c>
       <c r="E16">
-        <v>-39.9324300403694</v>
+        <v>-38.12881582717242</v>
       </c>
       <c r="F16">
-        <v>-4.95888556224713</v>
+        <v>-4.231796674233387</v>
       </c>
       <c r="G16">
-        <v>-13.27302766054247</v>
+        <v>-16.04243308123716</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.5506602697675</v>
       </c>
       <c r="E17">
-        <v>-40.56456878404812</v>
+        <v>-38.95059347687035</v>
       </c>
       <c r="F17">
-        <v>-4.78593537404565</v>
+        <v>-4.288995380781314</v>
       </c>
       <c r="G17">
-        <v>-14.60492965244759</v>
+        <v>-16.60047684533718</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.19249943604022</v>
       </c>
       <c r="E18">
-        <v>-39.77584899460618</v>
+        <v>-38.78554192047579</v>
       </c>
       <c r="F18">
-        <v>-4.313496894999078</v>
+        <v>-4.196533086467255</v>
       </c>
       <c r="G18">
-        <v>-12.95440420511532</v>
+        <v>-15.64848478315497</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.93729391219955</v>
       </c>
       <c r="E19">
-        <v>-40.45313888837838</v>
+        <v>-37.59528913348473</v>
       </c>
       <c r="F19">
-        <v>-4.155820758499053</v>
+        <v>-4.386805058118854</v>
       </c>
       <c r="G19">
-        <v>-13.1437309939607</v>
+        <v>-14.84662596117871</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.77282065140073</v>
       </c>
       <c r="E20">
-        <v>-39.87312061629094</v>
+        <v>-39.27918634357793</v>
       </c>
       <c r="F20">
-        <v>-4.488770379778508</v>
+        <v>-3.741479739107419</v>
       </c>
       <c r="G20">
-        <v>-11.8089057903444</v>
+        <v>-14.88477668797327</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.68326250627173</v>
       </c>
       <c r="E21">
-        <v>-39.7285717259661</v>
+        <v>-41.14979027277037</v>
       </c>
       <c r="F21">
-        <v>-3.731399450955647</v>
+        <v>-3.830830843150598</v>
       </c>
       <c r="G21">
-        <v>-12.19067790193315</v>
+        <v>-14.06093087779794</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.65298917966202</v>
       </c>
       <c r="E22">
-        <v>-42.47576369000831</v>
+        <v>-38.82809599072587</v>
       </c>
       <c r="F22">
-        <v>-3.947549177265527</v>
+        <v>-3.152657087894075</v>
       </c>
       <c r="G22">
-        <v>-12.39555763372203</v>
+        <v>-13.98456652384357</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.67742014579191</v>
       </c>
       <c r="E23">
-        <v>-42.90207196885339</v>
+        <v>-39.86370591882899</v>
       </c>
       <c r="F23">
-        <v>-3.462382453776568</v>
+        <v>-3.63230380441477</v>
       </c>
       <c r="G23">
-        <v>-11.73400138697285</v>
+        <v>-14.43468484809057</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.74310777143274</v>
       </c>
       <c r="E24">
-        <v>-42.07216570831169</v>
+        <v>-41.18031671605608</v>
       </c>
       <c r="F24">
-        <v>-3.7785946790887</v>
+        <v>-3.253098092610118</v>
       </c>
       <c r="G24">
-        <v>-13.6697485405138</v>
+        <v>-13.68592221074591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.82664850860915</v>
       </c>
       <c r="E25">
-        <v>-42.29143441976309</v>
+        <v>-40.25071836447252</v>
       </c>
       <c r="F25">
-        <v>-3.135927610456331</v>
+        <v>-3.22170508210132</v>
       </c>
       <c r="G25">
-        <v>-12.71081426433574</v>
+        <v>-14.67136071451138</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.91325959272393</v>
       </c>
       <c r="E26">
-        <v>-41.53518152471915</v>
+        <v>-42.15878183065641</v>
       </c>
       <c r="F26">
-        <v>-3.113263195100477</v>
+        <v>-3.994307302565919</v>
       </c>
       <c r="G26">
-        <v>-13.33951003606212</v>
+        <v>-14.48701298615706</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.9888502806442</v>
       </c>
       <c r="E27">
-        <v>-42.53264132354465</v>
+        <v>-40.89069136818451</v>
       </c>
       <c r="F27">
-        <v>-3.161574935903914</v>
+        <v>-3.676529583956374</v>
       </c>
       <c r="G27">
-        <v>-14.14197137732653</v>
+        <v>-14.40553714989006</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.04815119521629</v>
       </c>
       <c r="E28">
-        <v>-42.65259380729682</v>
+        <v>-41.74862661859668</v>
       </c>
       <c r="F28">
-        <v>-4.124076165277027</v>
+        <v>-3.185908577294641</v>
       </c>
       <c r="G28">
-        <v>-12.85867978084729</v>
+        <v>-14.25127565939664</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.07894665272635</v>
       </c>
       <c r="E29">
-        <v>-40.89102421102407</v>
+        <v>-40.56008559478052</v>
       </c>
       <c r="F29">
-        <v>-3.302772612353792</v>
+        <v>-3.217851925609055</v>
       </c>
       <c r="G29">
-        <v>-12.534776005285</v>
+        <v>-13.94291986095954</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.06904398029969</v>
       </c>
       <c r="E30">
-        <v>-42.18698516677618</v>
+        <v>-40.82684667738737</v>
       </c>
       <c r="F30">
-        <v>-2.903526685895168</v>
+        <v>-3.436613182973494</v>
       </c>
       <c r="G30">
-        <v>-12.28042017041171</v>
+        <v>-14.47444615528999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.01574804428724</v>
       </c>
       <c r="E31">
-        <v>-42.90624495765147</v>
+        <v>-41.40227986954203</v>
       </c>
       <c r="F31">
-        <v>-3.561435340257728</v>
+        <v>-3.352980840990968</v>
       </c>
       <c r="G31">
-        <v>-12.28157224025938</v>
+        <v>-14.38616052684871</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.92514103724656</v>
       </c>
       <c r="E32">
-        <v>-41.65639066000846</v>
+        <v>-40.93217898280578</v>
       </c>
       <c r="F32">
-        <v>-3.463519554623853</v>
+        <v>-3.28969516075705</v>
       </c>
       <c r="G32">
-        <v>-13.30361710132534</v>
+        <v>-14.7968005955399</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.80456371069299</v>
       </c>
       <c r="E33">
-        <v>-41.65241918830372</v>
+        <v>-40.1799836004727</v>
       </c>
       <c r="F33">
-        <v>-3.309616597467363</v>
+        <v>-3.217395026452451</v>
       </c>
       <c r="G33">
-        <v>-13.45458459900718</v>
+        <v>-15.77825982356717</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.65578909495801</v>
       </c>
       <c r="E34">
-        <v>-42.83402485417714</v>
+        <v>-39.03835756737601</v>
       </c>
       <c r="F34">
-        <v>-2.778323647338272</v>
+        <v>-3.298837103153924</v>
       </c>
       <c r="G34">
-        <v>-13.20207935909035</v>
+        <v>-15.84305382086178</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.48615120555234</v>
       </c>
       <c r="E35">
-        <v>-42.73360141458304</v>
+        <v>-38.8761725350283</v>
       </c>
       <c r="F35">
-        <v>-3.373127163941274</v>
+        <v>-3.245937366313458</v>
       </c>
       <c r="G35">
-        <v>-12.56831514214335</v>
+        <v>-14.55861346508042</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.30207259193295</v>
       </c>
       <c r="E36">
-        <v>-40.05385880664807</v>
+        <v>-39.71376361596102</v>
       </c>
       <c r="F36">
-        <v>-3.238965101020736</v>
+        <v>-3.461865373795177</v>
       </c>
       <c r="G36">
-        <v>-13.37624715991141</v>
+        <v>-14.92728905851582</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.11992907689609</v>
       </c>
       <c r="E37">
-        <v>-40.51157658121036</v>
+        <v>-39.74064010919654</v>
       </c>
       <c r="F37">
-        <v>-3.152220776914371</v>
+        <v>-2.968641546461419</v>
       </c>
       <c r="G37">
-        <v>-12.30275642116518</v>
+        <v>-14.95221084533545</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.94609113923223</v>
       </c>
       <c r="E38">
-        <v>-40.43647183979314</v>
+        <v>-38.89036250833134</v>
       </c>
       <c r="F38">
-        <v>-3.465051790097041</v>
+        <v>-2.854117436892331</v>
       </c>
       <c r="G38">
-        <v>-13.52848590708033</v>
+        <v>-15.33472286385223</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.77912302220506</v>
       </c>
       <c r="E39">
-        <v>-39.40528623079552</v>
+        <v>-38.98259167420856</v>
       </c>
       <c r="F39">
-        <v>-3.312853692358521</v>
+        <v>-3.371936217092863</v>
       </c>
       <c r="G39">
-        <v>-14.16226998730057</v>
+        <v>-15.56042261653758</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.62476726176106</v>
       </c>
       <c r="E40">
-        <v>-38.57797705009722</v>
+        <v>-37.74486236572108</v>
       </c>
       <c r="F40">
-        <v>-3.243413730937206</v>
+        <v>-3.145976224489794</v>
       </c>
       <c r="G40">
-        <v>-13.77777660727853</v>
+        <v>-15.21451530004853</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.48970778271491</v>
       </c>
       <c r="E41">
-        <v>-39.84780644658806</v>
+        <v>-37.12153376822428</v>
       </c>
       <c r="F41">
-        <v>-3.197454585271153</v>
+        <v>-2.971257036780767</v>
       </c>
       <c r="G41">
-        <v>-13.43640308290551</v>
+        <v>-14.98242122865407</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.38235230800939</v>
       </c>
       <c r="E42">
-        <v>-38.10615534323804</v>
+        <v>-36.33199432498696</v>
       </c>
       <c r="F42">
-        <v>-3.505829841860733</v>
+        <v>-3.059860631631858</v>
       </c>
       <c r="G42">
-        <v>-13.4760236919195</v>
+        <v>-15.99282455633118</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.3020951814593</v>
       </c>
       <c r="E43">
-        <v>-38.5062913065558</v>
+        <v>-36.58889012696809</v>
       </c>
       <c r="F43">
-        <v>-3.702322610348179</v>
+        <v>-3.047309762252</v>
       </c>
       <c r="G43">
-        <v>-11.72111012264292</v>
+        <v>-15.46895224328752</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.24883178435299</v>
       </c>
       <c r="E44">
-        <v>-38.75677026086806</v>
+        <v>-36.86135255835059</v>
       </c>
       <c r="F44">
-        <v>-3.531273661098183</v>
+        <v>-3.182592297107711</v>
       </c>
       <c r="G44">
-        <v>-14.35556280970199</v>
+        <v>-16.50588131709804</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.22431643773429</v>
       </c>
       <c r="E45">
-        <v>-37.64280867548423</v>
+        <v>-35.50744072072232</v>
       </c>
       <c r="F45">
-        <v>-3.248797539196742</v>
+        <v>-3.060468774703387</v>
       </c>
       <c r="G45">
-        <v>-13.39358779744611</v>
+        <v>-16.54477691663894</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.23883315116814</v>
       </c>
       <c r="E46">
-        <v>-38.19709615826008</v>
+        <v>-35.26498169387764</v>
       </c>
       <c r="F46">
-        <v>-3.57734604173719</v>
+        <v>-2.995141697544467</v>
       </c>
       <c r="G46">
-        <v>-13.52291591421051</v>
+        <v>-16.18255026591404</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.29539933604883</v>
       </c>
       <c r="E47">
-        <v>-35.960666249069</v>
+        <v>-35.59805774985281</v>
       </c>
       <c r="F47">
-        <v>-3.305396021202717</v>
+        <v>-2.976959961782265</v>
       </c>
       <c r="G47">
-        <v>-13.55534436304044</v>
+        <v>-16.02679737465518</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.38638287855491</v>
       </c>
       <c r="E48">
-        <v>-34.77328451459881</v>
+        <v>-34.41544449851269</v>
       </c>
       <c r="F48">
-        <v>-3.551813534968475</v>
+        <v>-2.877281511464506</v>
       </c>
       <c r="G48">
-        <v>-12.91757107544539</v>
+        <v>-16.15289108842771</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.51268757304018</v>
       </c>
       <c r="E49">
-        <v>-35.49846754947612</v>
+        <v>-34.96613863716346</v>
       </c>
       <c r="F49">
-        <v>-3.353334007410111</v>
+        <v>-2.616734173521197</v>
       </c>
       <c r="G49">
-        <v>-13.55829736966147</v>
+        <v>-16.22028220869789</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.67310270266037</v>
       </c>
       <c r="E50">
-        <v>-35.790633371266</v>
+        <v>-32.88577805617273</v>
       </c>
       <c r="F50">
-        <v>-3.266726673865432</v>
+        <v>-3.010453758187894</v>
       </c>
       <c r="G50">
-        <v>-15.88020972872179</v>
+        <v>-16.53209752722353</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.87009831899251</v>
       </c>
       <c r="E51">
-        <v>-34.75311016289464</v>
+        <v>-33.9993479285549</v>
       </c>
       <c r="F51">
-        <v>-3.413791188879054</v>
+        <v>-2.795468055725862</v>
       </c>
       <c r="G51">
-        <v>-13.99266080768709</v>
+        <v>-15.97245311435528</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.09621411761583</v>
       </c>
       <c r="E52">
-        <v>-35.30895544072913</v>
+        <v>-33.55709262849181</v>
       </c>
       <c r="F52">
-        <v>-3.719352200056899</v>
+        <v>-2.826994097531557</v>
       </c>
       <c r="G52">
-        <v>-15.11629141389835</v>
+        <v>-16.5692120532643</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.33932292620797</v>
       </c>
       <c r="E53">
-        <v>-33.80282574204404</v>
+        <v>-32.98073109916557</v>
       </c>
       <c r="F53">
-        <v>-3.466225316180382</v>
+        <v>-2.586389576328419</v>
       </c>
       <c r="G53">
-        <v>-14.52057695210697</v>
+        <v>-16.00204608093082</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.59419260671574</v>
       </c>
       <c r="E54">
-        <v>-31.96265542242014</v>
+        <v>-31.43009102945908</v>
       </c>
       <c r="F54">
-        <v>-2.809763377171576</v>
+        <v>-2.896409511511184</v>
       </c>
       <c r="G54">
-        <v>-14.47882435176568</v>
+        <v>-16.3375185578801</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.85938028658632</v>
       </c>
       <c r="E55">
-        <v>-33.36618122127644</v>
+        <v>-30.64302639726695</v>
       </c>
       <c r="F55">
-        <v>-3.735476701834946</v>
+        <v>-3.411814723896586</v>
       </c>
       <c r="G55">
-        <v>-14.2784419960919</v>
+        <v>-16.45987632101156</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.13129741289244</v>
       </c>
       <c r="E56">
-        <v>-34.22596182484675</v>
+        <v>-31.68094358287698</v>
       </c>
       <c r="F56">
-        <v>-3.519022903989302</v>
+        <v>-2.897718444450295</v>
       </c>
       <c r="G56">
-        <v>-14.97497084591794</v>
+        <v>-16.30862246114057</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.39720595337354</v>
       </c>
       <c r="E57">
-        <v>-32.54858335308759</v>
+        <v>-31.28044534163861</v>
       </c>
       <c r="F57">
-        <v>-3.333965284064287</v>
+        <v>-3.168972426234932</v>
       </c>
       <c r="G57">
-        <v>-14.65639539340111</v>
+        <v>-16.89729870311546</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.65293871083648</v>
       </c>
       <c r="E58">
-        <v>-34.70218520844138</v>
+        <v>-31.01942409983649</v>
       </c>
       <c r="F58">
-        <v>-3.486257612304775</v>
+        <v>-3.031277907270007</v>
       </c>
       <c r="G58">
-        <v>-14.62335945946472</v>
+        <v>-15.88864499875586</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.8960766174837</v>
       </c>
       <c r="E59">
-        <v>-31.18707726454846</v>
+        <v>-31.05537112650938</v>
       </c>
       <c r="F59">
-        <v>-3.222415374204394</v>
+        <v>-3.337702038171766</v>
       </c>
       <c r="G59">
-        <v>-14.15074597827836</v>
+        <v>-16.03611159452992</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.1336318047774</v>
       </c>
       <c r="E60">
-        <v>-32.84544746666042</v>
+        <v>-29.53807647515838</v>
       </c>
       <c r="F60">
-        <v>-3.572384291104119</v>
+        <v>-3.599950276268257</v>
       </c>
       <c r="G60">
-        <v>-15.41953241947728</v>
+        <v>-17.0003162592065</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.3652729754294</v>
       </c>
       <c r="E61">
-        <v>-31.34079857897584</v>
+        <v>-29.99765092406381</v>
       </c>
       <c r="F61">
-        <v>-3.366962588665425</v>
+        <v>-3.295006118544476</v>
       </c>
       <c r="G61">
-        <v>-13.7236789826213</v>
+        <v>-16.35381637356993</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.58315040836283</v>
       </c>
       <c r="E62">
-        <v>-31.4276207468879</v>
+        <v>-29.13760766900106</v>
       </c>
       <c r="F62">
-        <v>-3.568002176836098</v>
+        <v>-3.60478691413401</v>
       </c>
       <c r="G62">
-        <v>-14.65904714037806</v>
+        <v>-16.9620314553176</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.79148641127327</v>
       </c>
       <c r="E63">
-        <v>-31.80486074562287</v>
+        <v>-29.61303177693334</v>
       </c>
       <c r="F63">
-        <v>-3.452084406061422</v>
+        <v>-3.550088879226562</v>
       </c>
       <c r="G63">
-        <v>-15.45907192012557</v>
+        <v>-17.39372328309302</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.99432506877223</v>
       </c>
       <c r="E64">
-        <v>-31.59185944219809</v>
+        <v>-29.92208654253481</v>
       </c>
       <c r="F64">
-        <v>-3.753047918966747</v>
+        <v>-3.596669629464424</v>
       </c>
       <c r="G64">
-        <v>-14.60213389673968</v>
+        <v>-17.02579421767673</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.19553512075464</v>
       </c>
       <c r="E65">
-        <v>-29.01427467940216</v>
+        <v>-30.09892798100835</v>
       </c>
       <c r="F65">
-        <v>-3.773986886727729</v>
+        <v>-3.192264780986258</v>
       </c>
       <c r="G65">
-        <v>-15.36617801229362</v>
+        <v>-17.11314792754871</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.38740371843279</v>
       </c>
       <c r="E66">
-        <v>-30.03235714885859</v>
+        <v>-29.36523594347062</v>
       </c>
       <c r="F66">
-        <v>-3.499807800117275</v>
+        <v>-3.334541753017507</v>
       </c>
       <c r="G66">
-        <v>-14.91804104955186</v>
+        <v>-16.96337884735209</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.56308421863157</v>
       </c>
       <c r="E67">
-        <v>-29.93833244303733</v>
+        <v>-29.44958330033749</v>
       </c>
       <c r="F67">
-        <v>-3.50312249659829</v>
+        <v>-3.787347029830376</v>
       </c>
       <c r="G67">
-        <v>-15.31636754410974</v>
+        <v>-17.46857968355426</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.71599457531243</v>
       </c>
       <c r="E68">
-        <v>-30.08997065942118</v>
+        <v>-28.60712863832053</v>
       </c>
       <c r="F68">
-        <v>-3.29114345981672</v>
+        <v>-3.974361318413917</v>
       </c>
       <c r="G68">
-        <v>-14.70942205657638</v>
+        <v>-16.61646678029186</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.84807407143146</v>
       </c>
       <c r="E69">
-        <v>-30.64024591422624</v>
+        <v>-28.64332473106384</v>
       </c>
       <c r="F69">
-        <v>-3.472554596871435</v>
+        <v>-4.321709993876547</v>
       </c>
       <c r="G69">
-        <v>-15.02837822183023</v>
+        <v>-16.62031032366295</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.95278282495023</v>
       </c>
       <c r="E70">
-        <v>-30.23418217843244</v>
+        <v>-29.88893584856167</v>
       </c>
       <c r="F70">
-        <v>-3.528061113648715</v>
+        <v>-3.777007013908472</v>
       </c>
       <c r="G70">
-        <v>-15.02206832203238</v>
+        <v>-17.32169408852233</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.01329097909952</v>
       </c>
       <c r="E71">
-        <v>-29.51853837405228</v>
+        <v>-29.23004740891963</v>
       </c>
       <c r="F71">
-        <v>-3.775435977640357</v>
+        <v>-4.015829865956741</v>
       </c>
       <c r="G71">
-        <v>-15.53975322546314</v>
+        <v>-16.56401118622211</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.02507163489498</v>
       </c>
       <c r="E72">
-        <v>-29.32932514458979</v>
+        <v>-28.11845647967882</v>
       </c>
       <c r="F72">
-        <v>-3.842284204331055</v>
+        <v>-4.388192384500779</v>
       </c>
       <c r="G72">
-        <v>-15.04078780178419</v>
+        <v>-16.7811283495969</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.98374124726821</v>
       </c>
       <c r="E73">
-        <v>-29.95775506805623</v>
+        <v>-29.38332266865725</v>
       </c>
       <c r="F73">
-        <v>-3.635583659365645</v>
+        <v>-3.945974181732622</v>
       </c>
       <c r="G73">
-        <v>-14.23564822917851</v>
+        <v>-16.68500169404585</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.89259351806465</v>
       </c>
       <c r="E74">
-        <v>-28.82675509921853</v>
+        <v>-29.58131660922062</v>
       </c>
       <c r="F74">
-        <v>-3.584040366641753</v>
+        <v>-4.529636327220508</v>
       </c>
       <c r="G74">
-        <v>-13.30849684545022</v>
+        <v>-15.42769291423159</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.74713005850778</v>
       </c>
       <c r="E75">
-        <v>-28.98724874652438</v>
+        <v>-29.76390920968389</v>
       </c>
       <c r="F75">
-        <v>-3.940056664579583</v>
+        <v>-4.06079048504311</v>
       </c>
       <c r="G75">
-        <v>-16.03819558294689</v>
+        <v>-16.44598692720155</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.54341768651313</v>
       </c>
       <c r="E76">
-        <v>-30.39100323331807</v>
+        <v>-30.90436916072361</v>
       </c>
       <c r="F76">
-        <v>-4.032763641457577</v>
+        <v>-4.129550244773744</v>
       </c>
       <c r="G76">
-        <v>-14.8614538946491</v>
+        <v>-15.91248754772969</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.28327929859603</v>
       </c>
       <c r="E77">
-        <v>-32.08388720007949</v>
+        <v>-29.72578625125032</v>
       </c>
       <c r="F77">
-        <v>-3.716895872182052</v>
+        <v>-3.823272606669163</v>
       </c>
       <c r="G77">
-        <v>-15.01744680045956</v>
+        <v>-16.63731328555265</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.97895841099589</v>
       </c>
       <c r="E78">
-        <v>-30.36538792009368</v>
+        <v>-29.66509564259952</v>
       </c>
       <c r="F78">
-        <v>-4.099129629697025</v>
+        <v>-4.651203968848512</v>
       </c>
       <c r="G78">
-        <v>-14.72166114343507</v>
+        <v>-16.23053993405132</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.63977447666539</v>
       </c>
       <c r="E79">
-        <v>-29.77537757010832</v>
+        <v>-31.44087332607134</v>
       </c>
       <c r="F79">
-        <v>-4.48870703154189</v>
+        <v>-4.674459106510826</v>
       </c>
       <c r="G79">
-        <v>-14.77576538918338</v>
+        <v>-15.97904109997843</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.26772020006418</v>
       </c>
       <c r="E80">
-        <v>-31.27224880368473</v>
+        <v>-30.89382913747076</v>
       </c>
       <c r="F80">
-        <v>-4.278580138828427</v>
+        <v>-4.178827254332642</v>
       </c>
       <c r="G80">
-        <v>-15.60426417111415</v>
+        <v>-16.00305083150199</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.87082888968081</v>
       </c>
       <c r="E81">
-        <v>-31.372776398181</v>
+        <v>-32.3750726072467</v>
       </c>
       <c r="F81">
-        <v>-4.14954690751504</v>
+        <v>-4.549820659112783</v>
       </c>
       <c r="G81">
-        <v>-15.54665240236699</v>
+        <v>-15.81292785645442</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.45633095696727</v>
       </c>
       <c r="E82">
-        <v>-30.52336826432527</v>
+        <v>-32.59129365569093</v>
       </c>
       <c r="F82">
-        <v>-4.603698334356033</v>
+        <v>-4.970646162375184</v>
       </c>
       <c r="G82">
-        <v>-14.82854872726151</v>
+        <v>-15.39387900209347</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.04289405873511</v>
       </c>
       <c r="E83">
-        <v>-31.73570641905173</v>
+        <v>-31.33987929875228</v>
       </c>
       <c r="F83">
-        <v>-4.52834006392872</v>
+        <v>-4.811221614544514</v>
       </c>
       <c r="G83">
-        <v>-16.38927397156829</v>
+        <v>-14.9420905076219</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.63828736520012</v>
       </c>
       <c r="E84">
-        <v>-31.7334421820479</v>
+        <v>-33.88535491659682</v>
       </c>
       <c r="F84">
-        <v>-4.023841834182949</v>
+        <v>-4.758884093304029</v>
       </c>
       <c r="G84">
-        <v>-13.9201135127395</v>
+        <v>-15.62421186326103</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.24518466935517</v>
       </c>
       <c r="E85">
-        <v>-31.44264848788235</v>
+        <v>-33.17151344487171</v>
       </c>
       <c r="F85">
-        <v>-4.666643517818131</v>
+        <v>-4.538221596988104</v>
       </c>
       <c r="G85">
-        <v>-15.47802644861066</v>
+        <v>-14.73711311473961</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.87113402096006</v>
       </c>
       <c r="E86">
-        <v>-32.74149861005135</v>
+        <v>-33.66567184977372</v>
       </c>
       <c r="F86">
-        <v>-5.098554170635651</v>
+        <v>-5.221848843564443</v>
       </c>
       <c r="G86">
-        <v>-14.88368751849085</v>
+        <v>-15.61281862078763</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.52805789486454</v>
       </c>
       <c r="E87">
-        <v>-33.98374507136148</v>
+        <v>-34.01644065369685</v>
       </c>
       <c r="F87">
-        <v>-4.481474246626078</v>
+        <v>-4.592466692003736</v>
       </c>
       <c r="G87">
-        <v>-14.83040759858182</v>
+        <v>-15.76262577225796</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.22680735174483</v>
       </c>
       <c r="E88">
-        <v>-35.37609006789284</v>
+        <v>-35.43170652141804</v>
       </c>
       <c r="F88">
-        <v>-4.588654711865273</v>
+        <v>-4.61690564983784</v>
       </c>
       <c r="G88">
-        <v>-14.66151018625928</v>
+        <v>-15.21090515013795</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.968104996004874</v>
       </c>
       <c r="E89">
-        <v>-36.75352506375395</v>
+        <v>-36.43737417938245</v>
       </c>
       <c r="F89">
-        <v>-4.670888641524467</v>
+        <v>-4.781736177810862</v>
       </c>
       <c r="G89">
-        <v>-14.16379614879417</v>
+        <v>-14.48190646966274</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.753806148635919</v>
       </c>
       <c r="E90">
-        <v>-36.88590368018317</v>
+        <v>-37.92207061058924</v>
       </c>
       <c r="F90">
-        <v>-4.577153047654394</v>
+        <v>-4.961315758974372</v>
       </c>
       <c r="G90">
-        <v>-16.13402097885387</v>
+        <v>-15.45964629977663</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.583804167397128</v>
       </c>
       <c r="E91">
-        <v>-38.39451271838746</v>
+        <v>-38.25215787371934</v>
       </c>
       <c r="F91">
-        <v>-4.878981263989549</v>
+        <v>-5.314273920789489</v>
       </c>
       <c r="G91">
-        <v>-14.94679313756043</v>
+        <v>-15.16227489143883</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.469004431184796</v>
       </c>
       <c r="E92">
-        <v>-39.90694152441723</v>
+        <v>-40.32241995767296</v>
       </c>
       <c r="F92">
-        <v>-5.250417314573055</v>
+        <v>-4.793932297065662</v>
       </c>
       <c r="G92">
-        <v>-15.17421602919898</v>
+        <v>-14.22536733000631</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.409382476335105</v>
       </c>
       <c r="E93">
-        <v>-39.98880501329089</v>
+        <v>-41.63967606244614</v>
       </c>
       <c r="F93">
-        <v>-5.33087274248921</v>
+        <v>-5.232009900717902</v>
       </c>
       <c r="G93">
-        <v>-15.18163165120695</v>
+        <v>-15.70343321801579</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.394799500153296</v>
       </c>
       <c r="E94">
-        <v>-40.9416344365338</v>
+        <v>-41.71719674474645</v>
       </c>
       <c r="F94">
-        <v>-4.752682300939168</v>
+        <v>-4.923960887546902</v>
       </c>
       <c r="G94">
-        <v>-15.57376245978808</v>
+        <v>-15.30524742164333</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.422457713780693</v>
       </c>
       <c r="E95">
-        <v>-42.28495190922111</v>
+        <v>-42.80530527202049</v>
       </c>
       <c r="F95">
-        <v>-5.026760030371034</v>
+        <v>-5.319237255128476</v>
       </c>
       <c r="G95">
-        <v>-14.65886837091894</v>
+        <v>-15.40767073481007</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.489216325346119</v>
       </c>
       <c r="E96">
-        <v>-45.39036428116608</v>
+        <v>-44.70296456917175</v>
       </c>
       <c r="F96">
-        <v>-4.175695475884861</v>
+        <v>-5.23978906417454</v>
       </c>
       <c r="G96">
-        <v>-15.31613249537645</v>
+        <v>-16.74527183086105</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.590975131167582</v>
       </c>
       <c r="E97">
-        <v>-46.07929008890099</v>
+        <v>-46.46858035697037</v>
       </c>
       <c r="F97">
-        <v>-5.065373948001278</v>
+        <v>-5.661332778069593</v>
       </c>
       <c r="G97">
-        <v>-15.39758184727914</v>
+        <v>-15.12489883230045</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.720896114235195</v>
       </c>
       <c r="E98">
-        <v>-47.47058221522557</v>
+        <v>-47.1808391270298</v>
       </c>
       <c r="F98">
-        <v>-4.735621037112139</v>
+        <v>-5.323776156282126</v>
       </c>
       <c r="G98">
-        <v>-15.58926739982125</v>
+        <v>-15.30289693431045</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.860350211817751</v>
       </c>
       <c r="E99">
-        <v>-48.44069682375575</v>
+        <v>-49.96026703329561</v>
       </c>
       <c r="F99">
-        <v>-5.094559272463955</v>
+        <v>-5.464561277341031</v>
       </c>
       <c r="G99">
-        <v>-15.23108292519981</v>
+        <v>-16.20464815738868</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.01030418600428</v>
       </c>
       <c r="E100">
-        <v>-51.86206082721588</v>
+        <v>-50.21223132708239</v>
       </c>
       <c r="F100">
-        <v>-5.212139142596883</v>
+        <v>-5.619871357203388</v>
       </c>
       <c r="G100">
-        <v>-16.37466122355795</v>
+        <v>-16.10799015927858</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.15189573255449</v>
       </c>
       <c r="E101">
-        <v>-53.33904866354311</v>
+        <v>-52.87335964260883</v>
       </c>
       <c r="F101">
-        <v>-4.828760365705048</v>
+        <v>-5.232197569868882</v>
       </c>
       <c r="G101">
-        <v>-16.05214953239492</v>
+        <v>-16.2567892496322</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.30571055052991</v>
       </c>
       <c r="E102">
-        <v>-53.87320028664386</v>
+        <v>-53.78443540338251</v>
       </c>
       <c r="F102">
-        <v>-4.543498505098349</v>
+        <v>-5.650424211724046</v>
       </c>
       <c r="G102">
-        <v>-15.50504381075666</v>
+        <v>-16.42694963507797</v>
       </c>
     </row>
   </sheetData>
